--- a/05_Figures/Muscle_size/F1_Overview/c_data/f1_overview.xlsx
+++ b/05_Figures/Muscle_size/F1_Overview/c_data/f1_overview.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2842" uniqueCount="414">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2866" uniqueCount="427">
   <si>
     <t>sheet</t>
   </si>
@@ -800,7 +800,7 @@
     <t>03_Group_comparisons/Muscle_size/02_Protein_Contrasts/c_data/protein_contrasts.xlsx</t>
   </si>
   <si>
-    <t>23b313e174688029e3a472d568ce5203</t>
+    <t>67f4dd3b782bcc079a5d5276cc60dc17</t>
   </si>
   <si>
     <t>set_tests</t>
@@ -947,12 +947,24 @@
     <t>1.2.1</t>
   </si>
   <si>
+    <t>evaluate</t>
+  </si>
+  <si>
+    <t>1.0.5</t>
+  </si>
+  <si>
     <t>farver</t>
   </si>
   <si>
     <t>2.1.2</t>
   </si>
   <si>
+    <t>fastmap</t>
+  </si>
+  <si>
+    <t>1.2.0</t>
+  </si>
+  <si>
     <t>foreach</t>
   </si>
   <si>
@@ -1025,6 +1037,18 @@
     <t>1.1.4</t>
   </si>
   <si>
+    <t>htmltools</t>
+  </si>
+  <si>
+    <t>0.5.9</t>
+  </si>
+  <si>
+    <t>htmlwidgets</t>
+  </si>
+  <si>
+    <t>1.6.4</t>
+  </si>
+  <si>
     <t>IRanges</t>
   </si>
   <si>
@@ -1037,6 +1061,15 @@
     <t>1.0.14</t>
   </si>
   <si>
+    <t>jsonlite</t>
+  </si>
+  <si>
+    <t>knitr</t>
+  </si>
+  <si>
+    <t>1.51</t>
+  </si>
+  <si>
     <t>labeling</t>
   </si>
   <si>
@@ -1046,9 +1079,6 @@
     <t>lifecycle</t>
   </si>
   <si>
-    <t>1.0.5</t>
-  </si>
-  <si>
     <t>limma</t>
   </si>
   <si>
@@ -1085,6 +1115,9 @@
     <t>1.5.0</t>
   </si>
   <si>
+    <t>otel</t>
+  </si>
+  <si>
     <t>patchwork</t>
   </si>
   <si>
@@ -1161,6 +1194,12 @@
   </si>
   <si>
     <t>1.3.0</t>
+  </si>
+  <si>
+    <t>rmarkdown</t>
+  </si>
+  <si>
+    <t>2.31</t>
   </si>
   <si>
     <t>rprojroot</t>
@@ -1793,7 +1832,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C73"/>
+  <dimension ref="A1:C81"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3" s="1" customFormat="1">
@@ -2068,15 +2107,15 @@
         <v>320</v>
       </c>
       <c r="C25" t="s">
-        <v>321</v>
+        <v>277</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" t="s">
+        <v>321</v>
+      </c>
+      <c r="B26" t="s">
         <v>322</v>
-      </c>
-      <c r="B26" t="s">
-        <v>312</v>
       </c>
       <c r="C26" t="s">
         <v>277</v>
@@ -2090,15 +2129,15 @@
         <v>324</v>
       </c>
       <c r="C27" t="s">
-        <v>277</v>
+        <v>325</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B28" t="s">
-        <v>326</v>
+        <v>316</v>
       </c>
       <c r="C28" t="s">
         <v>277</v>
@@ -2145,7 +2184,7 @@
         <v>334</v>
       </c>
       <c r="C32" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -2200,7 +2239,7 @@
         <v>344</v>
       </c>
       <c r="C37" t="s">
-        <v>321</v>
+        <v>277</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -2208,7 +2247,7 @@
         <v>345</v>
       </c>
       <c r="B38" t="s">
-        <v>346</v>
+        <v>296</v>
       </c>
       <c r="C38" t="s">
         <v>277</v>
@@ -2216,10 +2255,10 @@
     </row>
     <row r="39" spans="1:3">
       <c r="A39" t="s">
+        <v>346</v>
+      </c>
+      <c r="B39" t="s">
         <v>347</v>
-      </c>
-      <c r="B39" t="s">
-        <v>348</v>
       </c>
       <c r="C39" t="s">
         <v>277</v>
@@ -2227,10 +2266,10 @@
     </row>
     <row r="40" spans="1:3">
       <c r="A40" t="s">
+        <v>348</v>
+      </c>
+      <c r="B40" t="s">
         <v>349</v>
-      </c>
-      <c r="B40" t="s">
-        <v>350</v>
       </c>
       <c r="C40" t="s">
         <v>277</v>
@@ -2238,10 +2277,10 @@
     </row>
     <row r="41" spans="1:3">
       <c r="A41" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B41" t="s">
-        <v>352</v>
+        <v>308</v>
       </c>
       <c r="C41" t="s">
         <v>277</v>
@@ -2249,32 +2288,32 @@
     </row>
     <row r="42" spans="1:3">
       <c r="A42" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="B42" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C42" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B43" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="C43" t="s">
-        <v>277</v>
+        <v>325</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="B44" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="C44" t="s">
         <v>277</v>
@@ -2282,10 +2321,10 @@
     </row>
     <row r="45" spans="1:3">
       <c r="A45" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="B45" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="C45" t="s">
         <v>277</v>
@@ -2293,10 +2332,10 @@
     </row>
     <row r="46" spans="1:3">
       <c r="A46" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="B46" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="C46" t="s">
         <v>277</v>
@@ -2304,10 +2343,10 @@
     </row>
     <row r="47" spans="1:3">
       <c r="A47" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="B47" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="C47" t="s">
         <v>277</v>
@@ -2315,10 +2354,10 @@
     </row>
     <row r="48" spans="1:3">
       <c r="A48" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="B48" t="s">
-        <v>366</v>
+        <v>324</v>
       </c>
       <c r="C48" t="s">
         <v>277</v>
@@ -2326,10 +2365,10 @@
     </row>
     <row r="49" spans="1:3">
       <c r="A49" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="B49" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="C49" t="s">
         <v>277</v>
@@ -2337,10 +2376,10 @@
     </row>
     <row r="50" spans="1:3">
       <c r="A50" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="B50" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="C50" t="s">
         <v>277</v>
@@ -2348,10 +2387,10 @@
     </row>
     <row r="51" spans="1:3">
       <c r="A51" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="B51" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="C51" t="s">
         <v>277</v>
@@ -2359,10 +2398,10 @@
     </row>
     <row r="52" spans="1:3">
       <c r="A52" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="B52" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="C52" t="s">
         <v>277</v>
@@ -2370,10 +2409,10 @@
     </row>
     <row r="53" spans="1:3">
       <c r="A53" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="B53" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="C53" t="s">
         <v>277</v>
@@ -2381,21 +2420,21 @@
     </row>
     <row r="54" spans="1:3">
       <c r="A54" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="B54" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="C54" t="s">
-        <v>321</v>
+        <v>277</v>
       </c>
     </row>
     <row r="55" spans="1:3">
       <c r="A55" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="B55" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="C55" t="s">
         <v>277</v>
@@ -2403,21 +2442,21 @@
     </row>
     <row r="56" spans="1:3">
       <c r="A56" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="B56" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="C56" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
     </row>
     <row r="57" spans="1:3">
       <c r="A57" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="B57" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="C57" t="s">
         <v>277</v>
@@ -2425,10 +2464,10 @@
     </row>
     <row r="58" spans="1:3">
       <c r="A58" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="B58" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="C58" t="s">
         <v>277</v>
@@ -2436,10 +2475,10 @@
     </row>
     <row r="59" spans="1:3">
       <c r="A59" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="B59" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="C59" t="s">
         <v>277</v>
@@ -2447,10 +2486,10 @@
     </row>
     <row r="60" spans="1:3">
       <c r="A60" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="B60" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="C60" t="s">
         <v>277</v>
@@ -2458,21 +2497,21 @@
     </row>
     <row r="61" spans="1:3">
       <c r="A61" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="B61" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="C61" t="s">
-        <v>277</v>
+        <v>325</v>
       </c>
     </row>
     <row r="62" spans="1:3">
       <c r="A62" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="B62" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="C62" t="s">
         <v>277</v>
@@ -2480,10 +2519,10 @@
     </row>
     <row r="63" spans="1:3">
       <c r="A63" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="B63" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="C63" t="s">
         <v>277</v>
@@ -2491,21 +2530,21 @@
     </row>
     <row r="64" spans="1:3">
       <c r="A64" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="B64" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="C64" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
     </row>
     <row r="65" spans="1:3">
       <c r="A65" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="B65" t="s">
-        <v>354</v>
+        <v>397</v>
       </c>
       <c r="C65" t="s">
         <v>277</v>
@@ -2513,10 +2552,10 @@
     </row>
     <row r="66" spans="1:3">
       <c r="A66" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="B66" t="s">
-        <v>306</v>
+        <v>399</v>
       </c>
       <c r="C66" t="s">
         <v>277</v>
@@ -2524,10 +2563,10 @@
     </row>
     <row r="67" spans="1:3">
       <c r="A67" t="s">
+        <v>400</v>
+      </c>
+      <c r="B67" t="s">
         <v>401</v>
-      </c>
-      <c r="B67" t="s">
-        <v>402</v>
       </c>
       <c r="C67" t="s">
         <v>277</v>
@@ -2535,10 +2574,10 @@
     </row>
     <row r="68" spans="1:3">
       <c r="A68" t="s">
+        <v>402</v>
+      </c>
+      <c r="B68" t="s">
         <v>403</v>
-      </c>
-      <c r="B68" t="s">
-        <v>404</v>
       </c>
       <c r="C68" t="s">
         <v>277</v>
@@ -2546,10 +2585,10 @@
     </row>
     <row r="69" spans="1:3">
       <c r="A69" t="s">
+        <v>404</v>
+      </c>
+      <c r="B69" t="s">
         <v>405</v>
-      </c>
-      <c r="B69" t="s">
-        <v>406</v>
       </c>
       <c r="C69" t="s">
         <v>277</v>
@@ -2557,10 +2596,10 @@
     </row>
     <row r="70" spans="1:3">
       <c r="A70" t="s">
+        <v>406</v>
+      </c>
+      <c r="B70" t="s">
         <v>407</v>
-      </c>
-      <c r="B70" t="s">
-        <v>408</v>
       </c>
       <c r="C70" t="s">
         <v>277</v>
@@ -2568,10 +2607,10 @@
     </row>
     <row r="71" spans="1:3">
       <c r="A71" t="s">
+        <v>408</v>
+      </c>
+      <c r="B71" t="s">
         <v>409</v>
-      </c>
-      <c r="B71" t="s">
-        <v>410</v>
       </c>
       <c r="C71" t="s">
         <v>277</v>
@@ -2579,10 +2618,10 @@
     </row>
     <row r="72" spans="1:3">
       <c r="A72" t="s">
+        <v>410</v>
+      </c>
+      <c r="B72" t="s">
         <v>411</v>
-      </c>
-      <c r="B72" t="s">
-        <v>310</v>
       </c>
       <c r="C72" t="s">
         <v>277</v>
@@ -2593,9 +2632,97 @@
         <v>412</v>
       </c>
       <c r="B73" t="s">
+        <v>365</v>
+      </c>
+      <c r="C73" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3">
+      <c r="A74" t="s">
         <v>413</v>
       </c>
-      <c r="C73" t="s">
+      <c r="B74" t="s">
+        <v>306</v>
+      </c>
+      <c r="C74" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3">
+      <c r="A75" t="s">
+        <v>414</v>
+      </c>
+      <c r="B75" t="s">
+        <v>415</v>
+      </c>
+      <c r="C75" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3">
+      <c r="A76" t="s">
+        <v>416</v>
+      </c>
+      <c r="B76" t="s">
+        <v>417</v>
+      </c>
+      <c r="C76" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3">
+      <c r="A77" t="s">
+        <v>418</v>
+      </c>
+      <c r="B77" t="s">
+        <v>419</v>
+      </c>
+      <c r="C77" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3">
+      <c r="A78" t="s">
+        <v>420</v>
+      </c>
+      <c r="B78" t="s">
+        <v>421</v>
+      </c>
+      <c r="C78" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3">
+      <c r="A79" t="s">
+        <v>422</v>
+      </c>
+      <c r="B79" t="s">
+        <v>423</v>
+      </c>
+      <c r="C79" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3">
+      <c r="A80" t="s">
+        <v>424</v>
+      </c>
+      <c r="B80" t="s">
+        <v>314</v>
+      </c>
+      <c r="C80" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3">
+      <c r="A81" t="s">
+        <v>425</v>
+      </c>
+      <c r="B81" t="s">
+        <v>426</v>
+      </c>
+      <c r="C81" t="s">
         <v>277</v>
       </c>
     </row>

--- a/05_Figures/Muscle_size/F1_Overview/c_data/f1_overview.xlsx
+++ b/05_Figures/Muscle_size/F1_Overview/c_data/f1_overview.xlsx
@@ -800,7 +800,7 @@
     <t>03_Group_comparisons/Muscle_size/02_Protein_Contrasts/c_data/protein_contrasts.xlsx</t>
   </si>
   <si>
-    <t>67f4dd3b782bcc079a5d5276cc60dc17</t>
+    <t>ad0b8c6478cbd0f38f1d2d7e66d6699d</t>
   </si>
   <si>
     <t>set_tests</t>
@@ -830,7 +830,7 @@
     <t>02_Groups/Muscle_size/c_data/clustering.xlsx</t>
   </si>
   <si>
-    <t>aed872f79b2de01ebea7891979b633ec</t>
+    <t>f076021f647b8c96d261ffcd843ac5ee</t>
   </si>
   <si>
     <t>design</t>

--- a/05_Figures/Muscle_size/F1_Overview/c_data/f1_overview.xlsx
+++ b/05_Figures/Muscle_size/F1_Overview/c_data/f1_overview.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2866" uniqueCount="427">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2842" uniqueCount="414">
   <si>
     <t>sheet</t>
   </si>
@@ -797,16 +797,16 @@
     <t>contrasts</t>
   </si>
   <si>
-    <t>03_Group_comparisons/Muscle_size/02_Protein_Contrasts/c_data/protein_contrasts.xlsx</t>
-  </si>
-  <si>
-    <t>ad0b8c6478cbd0f38f1d2d7e66d6699d</t>
+    <t>03_Group_comparisons/Muscle_size/c_data/02_protein_contrasts.xlsx</t>
+  </si>
+  <si>
+    <t>90119a3b81aee975ac6613c29ad8db6d</t>
   </si>
   <si>
     <t>set_tests</t>
   </si>
   <si>
-    <t>03_Group_comparisons/Muscle_size/03_Set_Contrasts/c_data/set_tests.rds</t>
+    <t>03_Group_comparisons/Muscle_size/c_data/03_set_tests.rds</t>
   </si>
   <si>
     <t>f9643fbdf7ae8fd212d60bc86e32de0c</t>
@@ -830,13 +830,13 @@
     <t>02_Groups/Muscle_size/c_data/clustering.xlsx</t>
   </si>
   <si>
-    <t>f076021f647b8c96d261ffcd843ac5ee</t>
+    <t>40857e7d2a66ed9fe9c1b5fedba5a7ef</t>
   </si>
   <si>
     <t>design</t>
   </si>
   <si>
-    <t>03_Group_comparisons/Muscle_size/01_Design_Contrasts/c_data/design.rds</t>
+    <t>03_Group_comparisons/Muscle_size/c_data/01_design.rds</t>
   </si>
   <si>
     <t>c4dd3f50a2d661a4b677d8502617baaf</t>
@@ -947,138 +947,108 @@
     <t>1.2.1</t>
   </si>
   <si>
-    <t>evaluate</t>
+    <t>farver</t>
+  </si>
+  <si>
+    <t>2.1.2</t>
+  </si>
+  <si>
+    <t>foreach</t>
+  </si>
+  <si>
+    <t>1.5.2</t>
+  </si>
+  <si>
+    <t>generics</t>
+  </si>
+  <si>
+    <t>0.1.4</t>
+  </si>
+  <si>
+    <t>GetoptLong</t>
+  </si>
+  <si>
+    <t>1.1.1</t>
+  </si>
+  <si>
+    <t>ggh4x</t>
+  </si>
+  <si>
+    <t>0.3.1</t>
+  </si>
+  <si>
+    <t>ggplot2</t>
+  </si>
+  <si>
+    <t>4.0.3</t>
+  </si>
+  <si>
+    <t>ggtext</t>
+  </si>
+  <si>
+    <t>0.2.0</t>
+  </si>
+  <si>
+    <t>CRAN (R 4.6.1)</t>
+  </si>
+  <si>
+    <t>GlobalOptions</t>
+  </si>
+  <si>
+    <t>glue</t>
+  </si>
+  <si>
+    <t>1.8.1</t>
+  </si>
+  <si>
+    <t>gridtext</t>
+  </si>
+  <si>
+    <t>0.1.6</t>
+  </si>
+  <si>
+    <t>gtable</t>
+  </si>
+  <si>
+    <t>0.3.6</t>
+  </si>
+  <si>
+    <t>here</t>
+  </si>
+  <si>
+    <t>1.0.2</t>
+  </si>
+  <si>
+    <t>hms</t>
+  </si>
+  <si>
+    <t>1.1.4</t>
+  </si>
+  <si>
+    <t>IRanges</t>
+  </si>
+  <si>
+    <t>2.46.0</t>
+  </si>
+  <si>
+    <t>iterators</t>
+  </si>
+  <si>
+    <t>1.0.14</t>
+  </si>
+  <si>
+    <t>labeling</t>
+  </si>
+  <si>
+    <t>0.4.3</t>
+  </si>
+  <si>
+    <t>lifecycle</t>
   </si>
   <si>
     <t>1.0.5</t>
   </si>
   <si>
-    <t>farver</t>
-  </si>
-  <si>
-    <t>2.1.2</t>
-  </si>
-  <si>
-    <t>fastmap</t>
-  </si>
-  <si>
-    <t>1.2.0</t>
-  </si>
-  <si>
-    <t>foreach</t>
-  </si>
-  <si>
-    <t>1.5.2</t>
-  </si>
-  <si>
-    <t>generics</t>
-  </si>
-  <si>
-    <t>0.1.4</t>
-  </si>
-  <si>
-    <t>GetoptLong</t>
-  </si>
-  <si>
-    <t>1.1.1</t>
-  </si>
-  <si>
-    <t>ggh4x</t>
-  </si>
-  <si>
-    <t>0.3.1</t>
-  </si>
-  <si>
-    <t>ggplot2</t>
-  </si>
-  <si>
-    <t>4.0.3</t>
-  </si>
-  <si>
-    <t>ggtext</t>
-  </si>
-  <si>
-    <t>0.2.0</t>
-  </si>
-  <si>
-    <t>CRAN (R 4.6.1)</t>
-  </si>
-  <si>
-    <t>GlobalOptions</t>
-  </si>
-  <si>
-    <t>glue</t>
-  </si>
-  <si>
-    <t>1.8.1</t>
-  </si>
-  <si>
-    <t>gridtext</t>
-  </si>
-  <si>
-    <t>0.1.6</t>
-  </si>
-  <si>
-    <t>gtable</t>
-  </si>
-  <si>
-    <t>0.3.6</t>
-  </si>
-  <si>
-    <t>here</t>
-  </si>
-  <si>
-    <t>1.0.2</t>
-  </si>
-  <si>
-    <t>hms</t>
-  </si>
-  <si>
-    <t>1.1.4</t>
-  </si>
-  <si>
-    <t>htmltools</t>
-  </si>
-  <si>
-    <t>0.5.9</t>
-  </si>
-  <si>
-    <t>htmlwidgets</t>
-  </si>
-  <si>
-    <t>1.6.4</t>
-  </si>
-  <si>
-    <t>IRanges</t>
-  </si>
-  <si>
-    <t>2.46.0</t>
-  </si>
-  <si>
-    <t>iterators</t>
-  </si>
-  <si>
-    <t>1.0.14</t>
-  </si>
-  <si>
-    <t>jsonlite</t>
-  </si>
-  <si>
-    <t>knitr</t>
-  </si>
-  <si>
-    <t>1.51</t>
-  </si>
-  <si>
-    <t>labeling</t>
-  </si>
-  <si>
-    <t>0.4.3</t>
-  </si>
-  <si>
-    <t>lifecycle</t>
-  </si>
-  <si>
     <t>limma</t>
   </si>
   <si>
@@ -1115,9 +1085,6 @@
     <t>1.5.0</t>
   </si>
   <si>
-    <t>otel</t>
-  </si>
-  <si>
     <t>patchwork</t>
   </si>
   <si>
@@ -1194,12 +1161,6 @@
   </si>
   <si>
     <t>1.3.0</t>
-  </si>
-  <si>
-    <t>rmarkdown</t>
-  </si>
-  <si>
-    <t>2.31</t>
   </si>
   <si>
     <t>rprojroot</t>
@@ -1832,7 +1793,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C81"/>
+  <dimension ref="A1:C73"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:3" s="1" customFormat="1">
@@ -2107,15 +2068,15 @@
         <v>320</v>
       </c>
       <c r="C25" t="s">
-        <v>277</v>
+        <v>321</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B26" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="C26" t="s">
         <v>277</v>
@@ -2129,15 +2090,15 @@
         <v>324</v>
       </c>
       <c r="C27" t="s">
-        <v>325</v>
+        <v>277</v>
       </c>
     </row>
     <row r="28" spans="1:3">
       <c r="A28" t="s">
+        <v>325</v>
+      </c>
+      <c r="B28" t="s">
         <v>326</v>
-      </c>
-      <c r="B28" t="s">
-        <v>316</v>
       </c>
       <c r="C28" t="s">
         <v>277</v>
@@ -2184,7 +2145,7 @@
         <v>334</v>
       </c>
       <c r="C32" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -2239,7 +2200,7 @@
         <v>344</v>
       </c>
       <c r="C37" t="s">
-        <v>277</v>
+        <v>321</v>
       </c>
     </row>
     <row r="38" spans="1:3">
@@ -2247,7 +2208,7 @@
         <v>345</v>
       </c>
       <c r="B38" t="s">
-        <v>296</v>
+        <v>346</v>
       </c>
       <c r="C38" t="s">
         <v>277</v>
@@ -2255,10 +2216,10 @@
     </row>
     <row r="39" spans="1:3">
       <c r="A39" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B39" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="C39" t="s">
         <v>277</v>
@@ -2266,10 +2227,10 @@
     </row>
     <row r="40" spans="1:3">
       <c r="A40" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B40" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C40" t="s">
         <v>277</v>
@@ -2277,10 +2238,10 @@
     </row>
     <row r="41" spans="1:3">
       <c r="A41" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B41" t="s">
-        <v>308</v>
+        <v>352</v>
       </c>
       <c r="C41" t="s">
         <v>277</v>
@@ -2288,32 +2249,32 @@
     </row>
     <row r="42" spans="1:3">
       <c r="A42" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="B42" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="C42" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
     </row>
     <row r="43" spans="1:3">
       <c r="A43" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="B43" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="C43" t="s">
-        <v>325</v>
+        <v>277</v>
       </c>
     </row>
     <row r="44" spans="1:3">
       <c r="A44" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="B44" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="C44" t="s">
         <v>277</v>
@@ -2321,10 +2282,10 @@
     </row>
     <row r="45" spans="1:3">
       <c r="A45" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="B45" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="C45" t="s">
         <v>277</v>
@@ -2332,10 +2293,10 @@
     </row>
     <row r="46" spans="1:3">
       <c r="A46" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="B46" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="C46" t="s">
         <v>277</v>
@@ -2343,10 +2304,10 @@
     </row>
     <row r="47" spans="1:3">
       <c r="A47" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="B47" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="C47" t="s">
         <v>277</v>
@@ -2354,10 +2315,10 @@
     </row>
     <row r="48" spans="1:3">
       <c r="A48" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="B48" t="s">
-        <v>324</v>
+        <v>366</v>
       </c>
       <c r="C48" t="s">
         <v>277</v>
@@ -2365,10 +2326,10 @@
     </row>
     <row r="49" spans="1:3">
       <c r="A49" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="B49" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="C49" t="s">
         <v>277</v>
@@ -2376,10 +2337,10 @@
     </row>
     <row r="50" spans="1:3">
       <c r="A50" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="B50" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="C50" t="s">
         <v>277</v>
@@ -2387,10 +2348,10 @@
     </row>
     <row r="51" spans="1:3">
       <c r="A51" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="B51" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="C51" t="s">
         <v>277</v>
@@ -2398,10 +2359,10 @@
     </row>
     <row r="52" spans="1:3">
       <c r="A52" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="B52" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="C52" t="s">
         <v>277</v>
@@ -2409,10 +2370,10 @@
     </row>
     <row r="53" spans="1:3">
       <c r="A53" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="B53" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="C53" t="s">
         <v>277</v>
@@ -2420,21 +2381,21 @@
     </row>
     <row r="54" spans="1:3">
       <c r="A54" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="B54" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="C54" t="s">
-        <v>277</v>
+        <v>321</v>
       </c>
     </row>
     <row r="55" spans="1:3">
       <c r="A55" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="B55" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="C55" t="s">
         <v>277</v>
@@ -2442,21 +2403,21 @@
     </row>
     <row r="56" spans="1:3">
       <c r="A56" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="B56" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="C56" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
     </row>
     <row r="57" spans="1:3">
       <c r="A57" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="B57" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="C57" t="s">
         <v>277</v>
@@ -2464,10 +2425,10 @@
     </row>
     <row r="58" spans="1:3">
       <c r="A58" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="B58" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="C58" t="s">
         <v>277</v>
@@ -2475,10 +2436,10 @@
     </row>
     <row r="59" spans="1:3">
       <c r="A59" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B59" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="C59" t="s">
         <v>277</v>
@@ -2486,10 +2447,10 @@
     </row>
     <row r="60" spans="1:3">
       <c r="A60" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="B60" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="C60" t="s">
         <v>277</v>
@@ -2497,21 +2458,21 @@
     </row>
     <row r="61" spans="1:3">
       <c r="A61" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="B61" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="C61" t="s">
-        <v>325</v>
+        <v>277</v>
       </c>
     </row>
     <row r="62" spans="1:3">
       <c r="A62" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="B62" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="C62" t="s">
         <v>277</v>
@@ -2519,10 +2480,10 @@
     </row>
     <row r="63" spans="1:3">
       <c r="A63" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="B63" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="C63" t="s">
         <v>277</v>
@@ -2530,21 +2491,21 @@
     </row>
     <row r="64" spans="1:3">
       <c r="A64" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="B64" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="C64" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
     </row>
     <row r="65" spans="1:3">
       <c r="A65" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="B65" t="s">
-        <v>397</v>
+        <v>354</v>
       </c>
       <c r="C65" t="s">
         <v>277</v>
@@ -2552,10 +2513,10 @@
     </row>
     <row r="66" spans="1:3">
       <c r="A66" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="B66" t="s">
-        <v>399</v>
+        <v>306</v>
       </c>
       <c r="C66" t="s">
         <v>277</v>
@@ -2563,10 +2524,10 @@
     </row>
     <row r="67" spans="1:3">
       <c r="A67" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B67" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C67" t="s">
         <v>277</v>
@@ -2574,10 +2535,10 @@
     </row>
     <row r="68" spans="1:3">
       <c r="A68" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B68" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C68" t="s">
         <v>277</v>
@@ -2585,10 +2546,10 @@
     </row>
     <row r="69" spans="1:3">
       <c r="A69" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B69" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C69" t="s">
         <v>277</v>
@@ -2596,10 +2557,10 @@
     </row>
     <row r="70" spans="1:3">
       <c r="A70" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B70" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C70" t="s">
         <v>277</v>
@@ -2607,10 +2568,10 @@
     </row>
     <row r="71" spans="1:3">
       <c r="A71" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B71" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C71" t="s">
         <v>277</v>
@@ -2618,10 +2579,10 @@
     </row>
     <row r="72" spans="1:3">
       <c r="A72" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="B72" t="s">
-        <v>411</v>
+        <v>310</v>
       </c>
       <c r="C72" t="s">
         <v>277</v>
@@ -2632,97 +2593,9 @@
         <v>412</v>
       </c>
       <c r="B73" t="s">
-        <v>365</v>
+        <v>413</v>
       </c>
       <c r="C73" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="74" spans="1:3">
-      <c r="A74" t="s">
-        <v>413</v>
-      </c>
-      <c r="B74" t="s">
-        <v>306</v>
-      </c>
-      <c r="C74" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="75" spans="1:3">
-      <c r="A75" t="s">
-        <v>414</v>
-      </c>
-      <c r="B75" t="s">
-        <v>415</v>
-      </c>
-      <c r="C75" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="76" spans="1:3">
-      <c r="A76" t="s">
-        <v>416</v>
-      </c>
-      <c r="B76" t="s">
-        <v>417</v>
-      </c>
-      <c r="C76" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="77" spans="1:3">
-      <c r="A77" t="s">
-        <v>418</v>
-      </c>
-      <c r="B77" t="s">
-        <v>419</v>
-      </c>
-      <c r="C77" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="78" spans="1:3">
-      <c r="A78" t="s">
-        <v>420</v>
-      </c>
-      <c r="B78" t="s">
-        <v>421</v>
-      </c>
-      <c r="C78" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="79" spans="1:3">
-      <c r="A79" t="s">
-        <v>422</v>
-      </c>
-      <c r="B79" t="s">
-        <v>423</v>
-      </c>
-      <c r="C79" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="80" spans="1:3">
-      <c r="A80" t="s">
-        <v>424</v>
-      </c>
-      <c r="B80" t="s">
-        <v>314</v>
-      </c>
-      <c r="C80" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="81" spans="1:3">
-      <c r="A81" t="s">
-        <v>425</v>
-      </c>
-      <c r="B81" t="s">
-        <v>426</v>
-      </c>
-      <c r="C81" t="s">
         <v>277</v>
       </c>
     </row>
